--- a/docs/seepage/files/xslope_earth_dam2.xlsx
+++ b/docs/seepage/files/xslope_earth_dam2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/PycharmProjects/xslope/docs/seepage/files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/seepage/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD69034-2B0C-A441-A1E6-EEF9306E68CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E611DB80-04F0-FE44-9951-34937B9ACC17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29280" yWindow="4060" windowWidth="38080" windowHeight="18420" activeTab="2" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
+    <workbookView xWindow="29280" yWindow="4060" windowWidth="38080" windowHeight="18420" activeTab="3" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -6398,16 +6398,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="M22:N22"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="M22:N22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6569,7 +6569,7 @@
         <v>0</v>
       </c>
       <c r="U4" s="3">
-        <v>0.01</v>
+        <v>1E-3</v>
       </c>
       <c r="V4" s="3">
         <v>-1</v>
@@ -6609,7 +6609,7 @@
         <v>0</v>
       </c>
       <c r="U5" s="3">
-        <v>0.01</v>
+        <v>1E-3</v>
       </c>
       <c r="V5" s="3">
         <v>-1</v>
@@ -6649,7 +6649,7 @@
         <v>0</v>
       </c>
       <c r="U6" s="3">
-        <v>0.01</v>
+        <v>1E-3</v>
       </c>
       <c r="V6" s="3">
         <v>-1</v>
